--- a/artfynd/A 7261-2025 artfynd.xlsx
+++ b/artfynd/A 7261-2025 artfynd.xlsx
@@ -999,7 +999,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122785744</v>
+        <v>122787057</v>
       </c>
       <c r="B5" t="n">
         <v>98347</v>
@@ -1034,7 +1034,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>51</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1048,10 +1048,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>392956</v>
+        <v>393020</v>
       </c>
       <c r="R5" t="n">
-        <v>6494751</v>
+        <v>6494783</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1110,7 +1110,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122787057</v>
+        <v>122785744</v>
       </c>
       <c r="B6" t="n">
         <v>98347</v>
@@ -1145,7 +1145,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>22</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1153,16 +1153,19 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Hagalund, Vg</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>393020</v>
+        <v>392956</v>
       </c>
       <c r="R6" t="n">
-        <v>6494783</v>
+        <v>6494751</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1203,6 +1206,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 7261-2025 artfynd.xlsx
+++ b/artfynd/A 7261-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122787057</v>
+        <v>122787634</v>
       </c>
       <c r="B2" t="n">
-        <v>98347</v>
+        <v>98355</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -710,7 +710,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>16</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -724,10 +724,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>393020</v>
+        <v>392962</v>
       </c>
       <c r="R2" t="n">
-        <v>6494783</v>
+        <v>6494847</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122787634</v>
+        <v>122787057</v>
       </c>
       <c r="B3" t="n">
-        <v>98347</v>
+        <v>98355</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -821,7 +821,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>51</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -835,10 +835,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>392962</v>
+        <v>393020</v>
       </c>
       <c r="R3" t="n">
-        <v>6494847</v>
+        <v>6494783</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -900,7 +900,7 @@
         <v>122785676</v>
       </c>
       <c r="B4" t="n">
-        <v>98347</v>
+        <v>98355</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
         <v>122785570</v>
       </c>
       <c r="B5" t="n">
-        <v>94758</v>
+        <v>94766</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1113,7 +1113,7 @@
         <v>122785744</v>
       </c>
       <c r="B6" t="n">
-        <v>98347</v>
+        <v>98355</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>

--- a/artfynd/A 7261-2025 artfynd.xlsx
+++ b/artfynd/A 7261-2025 artfynd.xlsx
@@ -786,7 +786,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122787057</v>
+        <v>122785676</v>
       </c>
       <c r="B3" t="n">
         <v>98355</v>
@@ -821,7 +821,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>13</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -835,10 +835,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>393020</v>
+        <v>392937</v>
       </c>
       <c r="R3" t="n">
-        <v>6494783</v>
+        <v>6494786</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -897,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122785676</v>
+        <v>122785570</v>
       </c>
       <c r="B4" t="n">
-        <v>98355</v>
+        <v>94766</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -909,47 +909,38 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>2810</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Hedw.) Warnst.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Hagalund, Vg</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>392937</v>
+        <v>392954</v>
       </c>
       <c r="R4" t="n">
-        <v>6494786</v>
+        <v>6494792</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -1008,10 +999,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122785570</v>
+        <v>122787057</v>
       </c>
       <c r="B5" t="n">
-        <v>94766</v>
+        <v>98355</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1020,38 +1011,47 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2810</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Hagalund, Vg</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>392954</v>
+        <v>393020</v>
       </c>
       <c r="R5" t="n">
-        <v>6494792</v>
+        <v>6494783</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>

--- a/artfynd/A 7261-2025 artfynd.xlsx
+++ b/artfynd/A 7261-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122787634</v>
+        <v>122787057</v>
       </c>
       <c r="B2" t="n">
-        <v>98355</v>
+        <v>98357</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -710,7 +710,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>51</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -724,10 +724,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>392962</v>
+        <v>393020</v>
       </c>
       <c r="R2" t="n">
-        <v>6494847</v>
+        <v>6494783</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122785676</v>
+        <v>122787634</v>
       </c>
       <c r="B3" t="n">
-        <v>98355</v>
+        <v>98357</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -821,7 +821,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>16</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -835,10 +835,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>392937</v>
+        <v>392962</v>
       </c>
       <c r="R3" t="n">
-        <v>6494786</v>
+        <v>6494847</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -900,7 +900,7 @@
         <v>122785570</v>
       </c>
       <c r="B4" t="n">
-        <v>94766</v>
+        <v>94768</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -999,10 +999,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122787057</v>
+        <v>122785676</v>
       </c>
       <c r="B5" t="n">
-        <v>98355</v>
+        <v>98357</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1034,7 +1034,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>13</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1048,10 +1048,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>393020</v>
+        <v>392937</v>
       </c>
       <c r="R5" t="n">
-        <v>6494783</v>
+        <v>6494786</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1113,7 +1113,7 @@
         <v>122785744</v>
       </c>
       <c r="B6" t="n">
-        <v>98355</v>
+        <v>98357</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>

--- a/artfynd/A 7261-2025 artfynd.xlsx
+++ b/artfynd/A 7261-2025 artfynd.xlsx
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122787634</v>
+        <v>122785570</v>
       </c>
       <c r="B3" t="n">
-        <v>98357</v>
+        <v>94768</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,47 +798,38 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>2810</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Hedw.) Warnst.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Hagalund, Vg</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>392962</v>
+        <v>392954</v>
       </c>
       <c r="R3" t="n">
-        <v>6494847</v>
+        <v>6494792</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -897,10 +888,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122785570</v>
+        <v>122787634</v>
       </c>
       <c r="B4" t="n">
-        <v>94768</v>
+        <v>98357</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -909,38 +900,47 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2810</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Hagalund, Vg</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>392954</v>
+        <v>392962</v>
       </c>
       <c r="R4" t="n">
-        <v>6494792</v>
+        <v>6494847</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>

--- a/artfynd/A 7261-2025 artfynd.xlsx
+++ b/artfynd/A 7261-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122787057</v>
+        <v>122787634</v>
       </c>
       <c r="B2" t="n">
-        <v>98357</v>
+        <v>98365</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -710,7 +710,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>16</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -724,10 +724,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>393020</v>
+        <v>392962</v>
       </c>
       <c r="R2" t="n">
-        <v>6494783</v>
+        <v>6494847</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122785570</v>
+        <v>122785676</v>
       </c>
       <c r="B3" t="n">
-        <v>94768</v>
+        <v>98365</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,38 +798,47 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2810</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Hagalund, Vg</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>392954</v>
+        <v>392937</v>
       </c>
       <c r="R3" t="n">
-        <v>6494792</v>
+        <v>6494786</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -888,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122787634</v>
+        <v>122785570</v>
       </c>
       <c r="B4" t="n">
-        <v>98357</v>
+        <v>94776</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -900,47 +909,38 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>2810</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Hedw.) Warnst.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Hagalund, Vg</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>392962</v>
+        <v>392954</v>
       </c>
       <c r="R4" t="n">
-        <v>6494847</v>
+        <v>6494792</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -999,10 +999,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122785676</v>
+        <v>122787057</v>
       </c>
       <c r="B5" t="n">
-        <v>98357</v>
+        <v>98365</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1034,7 +1034,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>51</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1048,10 +1048,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>392937</v>
+        <v>393020</v>
       </c>
       <c r="R5" t="n">
-        <v>6494786</v>
+        <v>6494783</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1113,7 +1113,7 @@
         <v>122785744</v>
       </c>
       <c r="B6" t="n">
-        <v>98357</v>
+        <v>98365</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>

--- a/artfynd/A 7261-2025 artfynd.xlsx
+++ b/artfynd/A 7261-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122787634</v>
+        <v>122785570</v>
       </c>
       <c r="B2" t="n">
-        <v>98365</v>
+        <v>94776</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,47 +687,38 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>2810</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Hedw.) Warnst.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Hagalund, Vg</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>392962</v>
+        <v>392954</v>
       </c>
       <c r="R2" t="n">
-        <v>6494847</v>
+        <v>6494792</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -897,10 +888,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122785570</v>
+        <v>122787057</v>
       </c>
       <c r="B4" t="n">
-        <v>94776</v>
+        <v>98365</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -909,38 +900,47 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2810</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Hagalund, Vg</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>392954</v>
+        <v>393020</v>
       </c>
       <c r="R4" t="n">
-        <v>6494792</v>
+        <v>6494783</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -999,7 +999,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122787057</v>
+        <v>122787634</v>
       </c>
       <c r="B5" t="n">
         <v>98365</v>
@@ -1034,7 +1034,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>16</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1048,10 +1048,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>393020</v>
+        <v>392962</v>
       </c>
       <c r="R5" t="n">
-        <v>6494783</v>
+        <v>6494847</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>

--- a/artfynd/A 7261-2025 artfynd.xlsx
+++ b/artfynd/A 7261-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122785570</v>
+        <v>122787057</v>
       </c>
       <c r="B2" t="n">
-        <v>94776</v>
+        <v>98365</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,38 +687,47 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2810</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Hagalund, Vg</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>392954</v>
+        <v>393020</v>
       </c>
       <c r="R2" t="n">
-        <v>6494792</v>
+        <v>6494783</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -777,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122785676</v>
+        <v>122785570</v>
       </c>
       <c r="B3" t="n">
-        <v>98365</v>
+        <v>94776</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,47 +798,38 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>2810</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Hedw.) Warnst.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Hagalund, Vg</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>392937</v>
+        <v>392954</v>
       </c>
       <c r="R3" t="n">
-        <v>6494786</v>
+        <v>6494792</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -888,7 +888,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122787057</v>
+        <v>122787634</v>
       </c>
       <c r="B4" t="n">
         <v>98365</v>
@@ -923,7 +923,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>16</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -937,10 +937,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>393020</v>
+        <v>392962</v>
       </c>
       <c r="R4" t="n">
-        <v>6494783</v>
+        <v>6494847</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -999,7 +999,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122787634</v>
+        <v>122785676</v>
       </c>
       <c r="B5" t="n">
         <v>98365</v>
@@ -1034,7 +1034,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>13</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1048,10 +1048,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>392962</v>
+        <v>392937</v>
       </c>
       <c r="R5" t="n">
-        <v>6494847</v>
+        <v>6494786</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>

--- a/artfynd/A 7261-2025 artfynd.xlsx
+++ b/artfynd/A 7261-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122787057</v>
+        <v>122785676</v>
       </c>
       <c r="B2" t="n">
         <v>98365</v>
@@ -710,7 +710,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>13</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -724,10 +724,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>393020</v>
+        <v>392937</v>
       </c>
       <c r="R2" t="n">
-        <v>6494783</v>
+        <v>6494786</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -999,7 +999,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122785676</v>
+        <v>122787057</v>
       </c>
       <c r="B5" t="n">
         <v>98365</v>
@@ -1034,7 +1034,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>51</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1048,10 +1048,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>392937</v>
+        <v>393020</v>
       </c>
       <c r="R5" t="n">
-        <v>6494786</v>
+        <v>6494783</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>

--- a/artfynd/A 7261-2025 artfynd.xlsx
+++ b/artfynd/A 7261-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122785676</v>
+        <v>122787057</v>
       </c>
       <c r="B2" t="n">
-        <v>98365</v>
+        <v>98368</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -710,7 +710,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>51</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -724,10 +724,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>392937</v>
+        <v>393020</v>
       </c>
       <c r="R2" t="n">
-        <v>6494786</v>
+        <v>6494783</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122785570</v>
+        <v>122787634</v>
       </c>
       <c r="B3" t="n">
-        <v>94776</v>
+        <v>98368</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,38 +798,47 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2810</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Hagalund, Vg</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>392954</v>
+        <v>392962</v>
       </c>
       <c r="R3" t="n">
-        <v>6494792</v>
+        <v>6494847</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -888,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122787634</v>
+        <v>122785570</v>
       </c>
       <c r="B4" t="n">
-        <v>98365</v>
+        <v>94779</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -900,47 +909,38 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>2810</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Hedw.) Warnst.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Hagalund, Vg</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>392962</v>
+        <v>392954</v>
       </c>
       <c r="R4" t="n">
-        <v>6494847</v>
+        <v>6494792</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -999,10 +999,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122787057</v>
+        <v>122785676</v>
       </c>
       <c r="B5" t="n">
-        <v>98365</v>
+        <v>98368</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1034,7 +1034,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>13</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1048,10 +1048,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>393020</v>
+        <v>392937</v>
       </c>
       <c r="R5" t="n">
-        <v>6494783</v>
+        <v>6494786</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1113,7 +1113,7 @@
         <v>122785744</v>
       </c>
       <c r="B6" t="n">
-        <v>98365</v>
+        <v>98368</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>

--- a/artfynd/A 7261-2025 artfynd.xlsx
+++ b/artfynd/A 7261-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122787057</v>
       </c>
       <c r="B2" t="n">
-        <v>98368</v>
+        <v>98370</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122787634</v>
+        <v>122785676</v>
       </c>
       <c r="B3" t="n">
-        <v>98368</v>
+        <v>98370</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -821,7 +821,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>13</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -835,10 +835,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>392962</v>
+        <v>392937</v>
       </c>
       <c r="R3" t="n">
-        <v>6494847</v>
+        <v>6494786</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -900,7 +900,7 @@
         <v>122785570</v>
       </c>
       <c r="B4" t="n">
-        <v>94779</v>
+        <v>94781</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -999,10 +999,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122785676</v>
+        <v>122787634</v>
       </c>
       <c r="B5" t="n">
-        <v>98368</v>
+        <v>98370</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1034,7 +1034,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>16</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1048,10 +1048,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>392937</v>
+        <v>392962</v>
       </c>
       <c r="R5" t="n">
-        <v>6494786</v>
+        <v>6494847</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1113,7 +1113,7 @@
         <v>122785744</v>
       </c>
       <c r="B6" t="n">
-        <v>98368</v>
+        <v>98370</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>

--- a/artfynd/A 7261-2025 artfynd.xlsx
+++ b/artfynd/A 7261-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122787057</v>
+        <v>122785570</v>
       </c>
       <c r="B2" t="n">
-        <v>98370</v>
+        <v>94787</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,47 +687,38 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>2810</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Hedw.) Warnst.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Hagalund, Vg</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>393020</v>
+        <v>392954</v>
       </c>
       <c r="R2" t="n">
-        <v>6494783</v>
+        <v>6494792</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -786,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122785676</v>
+        <v>122787634</v>
       </c>
       <c r="B3" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -821,7 +812,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>16</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -835,10 +826,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>392937</v>
+        <v>392962</v>
       </c>
       <c r="R3" t="n">
-        <v>6494786</v>
+        <v>6494847</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -897,10 +888,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122785570</v>
+        <v>122785676</v>
       </c>
       <c r="B4" t="n">
-        <v>94781</v>
+        <v>98376</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -909,38 +900,47 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2810</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Hagalund, Vg</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>392954</v>
+        <v>392937</v>
       </c>
       <c r="R4" t="n">
-        <v>6494792</v>
+        <v>6494786</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -999,10 +999,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122787634</v>
+        <v>122787057</v>
       </c>
       <c r="B5" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1034,7 +1034,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>51</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1048,10 +1048,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>392962</v>
+        <v>393020</v>
       </c>
       <c r="R5" t="n">
-        <v>6494847</v>
+        <v>6494783</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1113,7 +1113,7 @@
         <v>122785744</v>
       </c>
       <c r="B6" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>

--- a/artfynd/A 7261-2025 artfynd.xlsx
+++ b/artfynd/A 7261-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,12 +678,7 @@
         <v>122785570</v>
       </c>
       <c r="B2" t="n">
-        <v>94790</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96348</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -777,15 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122787057</v>
+        <v>122785676</v>
       </c>
       <c r="B3" t="n">
-        <v>98379</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -812,7 +802,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>13</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -826,10 +816,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>393020</v>
+        <v>392937</v>
       </c>
       <c r="R3" t="n">
-        <v>6494783</v>
+        <v>6494786</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -888,15 +878,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122785676</v>
+        <v>122785744</v>
       </c>
       <c r="B4" t="n">
-        <v>98379</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -923,7 +908,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>22</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -931,16 +916,19 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Hagalund, Vg</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>392937</v>
+        <v>392956</v>
       </c>
       <c r="R4" t="n">
-        <v>6494786</v>
+        <v>6494751</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -981,6 +969,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -999,15 +988,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122787634</v>
+        <v>122786962</v>
       </c>
       <c r="B5" t="n">
-        <v>98379</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1034,7 +1018,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>54</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1048,10 +1032,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>392962</v>
+        <v>393006</v>
       </c>
       <c r="R5" t="n">
-        <v>6494847</v>
+        <v>6494753</v>
       </c>
       <c r="S5" t="n">
         <v>15</v>
@@ -1110,15 +1094,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122785744</v>
+        <v>122787057</v>
       </c>
       <c r="B6" t="n">
-        <v>98379</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1145,7 +1124,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>51</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1153,19 +1132,16 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Hagalund, Vg</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>392956</v>
+        <v>393020</v>
       </c>
       <c r="R6" t="n">
-        <v>6494751</v>
+        <v>6494783</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1206,7 +1182,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1222,6 +1197,112 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>122787634</v>
+      </c>
+      <c r="B7" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Hagalund, Vg</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>392962</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6494847</v>
+      </c>
+      <c r="S7" t="n">
+        <v>15</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Lidköping</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Sunnersberg</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-02-27</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-02-27</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Jon Liljebäck</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Jon Liljebäck</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 7261-2025 artfynd.xlsx
+++ b/artfynd/A 7261-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AZ7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122785570</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -875,6 +885,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122785676</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -985,6 +1000,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122785744</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1091,6 +1111,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122786962</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1197,6 +1222,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122787057</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1303,8 +1333,21 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122787634</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>